--- a/stories/arbres/TREE-DIF-062.xlsx
+++ b/stories/arbres/TREE-DIF-062.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est avec maman, à la ferme. Tom a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom écoute maman. Tom entend les mots : laisser le temps.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-062.xlsx
+++ b/stories/arbres/TREE-DIF-062.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Tom est avec maman, à la ferme. Tom a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom écoute maman. Tom entend les mots : laisser le temps.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Tom a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Tom rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Tom rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Tom rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Tom a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Tom rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Tom rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Tom rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Tom a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Tom a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Tom rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Tom rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Tom rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Tom a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Tom a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Tom rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Tom rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Tom rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Tom respire. Tom retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Tom a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Tom rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Tom rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Tom rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Tom a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Tom rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Tom rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Tom rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Tom a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Tom répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Tom rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Tom rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Tom rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Tom a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Tom a entendu : laisser le temps. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-062.xlsx
+++ b/stories/arbres/TREE-DIF-062.xlsx
@@ -4221,17 +4221,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Tu as laissé la fin.</t>
+          <t>On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Le mot était long, cette fois.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Tu as laissé la fin.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Le mot était long, cette fois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Tu as laissé la fin. [pause]</t>
+          <t>On recule. Ils s'éloignent des abeilles, un pas. Près des. Nino attend, les lèvres fermées. Près des pots, le petit. Je l'entends, maintenant. Le seau rouge reste contre la jambe. Le mot est venu, tout seul. Le mot était long, cette fois. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4373,7 +4373,7 @@
 enfant-m|Je l'entends, maintenant.
 narrateur|Le seau rouge reste contre la jambe.
 maman|Le mot est venu, tout seul.
-papa|Tu as laissé la fin.</t>
+papa|Le mot était long, cette fois.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -15056,17 +15056,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Écouter d'abord, essuyer après.</t>
+          <t>Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Le linge peut attendre, un peu.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Écouter d'abord, essuyer après.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Le linge peut attendre, un peu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Écouter d'abord, essuyer après. [pause]</t>
+          <t>Mes mains, et le torchon. Une main écoute, l'autre tient le linge. Le bourdon s'éloigne, un peu. Près des. Nino ne frotte pas trop tôt. Près des feuilles. Le torchon dort contre sa poche. Tes mains ont deux métiers. Le linge peut attendre, un peu. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15208,7 +15208,7 @@
 maman|Près des feuilles.
 narrateur|Le torchon dort contre sa poche.
 papa|Tes mains ont deux métiers.
-maman|Écouter d'abord, essuyer après.</t>
+maman|Le linge peut attendre, un peu.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -15425,17 +15425,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le banc, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le mot d'abord, le tissu ensuite.</t>
+          <t>Le banc, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le thym a eu son mot, puis le linge.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt;, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le mot d'abord, le tissu ensuite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt;, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le thym a eu son mot, puis le linge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;banc&lt;/emphasis&gt;, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le mot d'abord, le tissu ensuite. [pause]</t>
+          <t>Le &lt;emphasis&gt;banc&lt;/emphasis&gt;, le torchon sur les genoux. On s'assoit, le thym est là. Le tissu attend, plié, sans bouger. Le petit pot. Nino lève le torchon, après le mot. Je l'essuie, contre le thym. Le torchon dort contre sa poche. Le banc a gardé le linge. Le thym a eu son mot, puis le linge. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15577,7 +15577,7 @@
 enfant-m|Je l'essuie, contre le thym.
 narrateur|Le torchon dort contre sa poche.
 papa|Le banc a gardé le linge.
-maman|Le mot d'abord, le tissu ensuite.</t>
+maman|Le thym a eu son mot, puis le linge.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -17281,7 +17281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17394,6 +17394,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
